--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -1,175 +1,192 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="Calc"/>
-  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <workbookPr/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
-  <extLst>
-    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
-      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
-    </ext>
-  </extLst>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$45</definedName>
+  </definedNames>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
-  <si>
-    <t xml:space="preserve">ID MUESTRAS</t>
-  </si>
-</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="General"/>
-  </numFmts>
-  <fonts count="5">
+  <numFmts count="0"/>
+  <fonts count="2">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <name val="Arial"/>
-      <family val="0"/>
-    </font>
-    <font>
-      <b val="true"/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
   <borders count="2">
-    <border diagonalUp="false" diagonalDown="false">
+    <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="20">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
-    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+  <cellStyleXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
-      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
-  <cellStyles count="6">
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Comma" xfId="15" builtinId="3"/>
-    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
-    <cellStyle name="Currency" xfId="17" builtinId="4"/>
-    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
-    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:srgbClr val="000000"/>
+        <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:srgbClr val="ffffff"/>
+        <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1f497d"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="eeece1"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4f81bd"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="c0504d"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9bbb59"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064a2"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4bacc6"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="f79646"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000ff"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -177,158 +194,486 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Times New Roman"/>
+        <a:font script="Hebr" typeface="Times New Roman"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="MoolBoran"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Times New Roman"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
+        <a:font script="Hang" typeface="맑은 고딕"/>
+        <a:font script="Hans" typeface="宋体"/>
+        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Arab" typeface="Arial"/>
+        <a:font script="Hebr" typeface="Arial"/>
+        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Ethi" typeface="Nyala"/>
+        <a:font script="Beng" typeface="Vrinda"/>
+        <a:font script="Gujr" typeface="Shruti"/>
+        <a:font script="Khmr" typeface="DaunPenh"/>
+        <a:font script="Knda" typeface="Tunga"/>
+        <a:font script="Guru" typeface="Raavi"/>
+        <a:font script="Cans" typeface="Euphemia"/>
+        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
+        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
+        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
+        <a:font script="Thaa" typeface="MV Boli"/>
+        <a:font script="Deva" typeface="Mangal"/>
+        <a:font script="Telu" typeface="Gautami"/>
+        <a:font script="Taml" typeface="Latha"/>
+        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
+        <a:font script="Orya" typeface="Kalinga"/>
+        <a:font script="Mlym" typeface="Kartika"/>
+        <a:font script="Laoo" typeface="DokChampa"/>
+        <a:font script="Sinh" typeface="Iskoola Pota"/>
+        <a:font script="Mong" typeface="Mongolian Baiti"/>
+        <a:font script="Viet" typeface="Arial"/>
+        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme>
+    <a:fmtScheme name="Office">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
+                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr">
+              <a:shade val="95000"/>
+              <a:satMod val="105000"/>
+            </a:schemeClr>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="38000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst/>
+          <a:effectLst>
+            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
+              <a:srgbClr val="000000">
+                <a:alpha val="35000"/>
+              </a:srgbClr>
+            </a:outerShdw>
+          </a:effectLst>
+          <a:scene3d>
+            <a:camera prst="orthographicFront">
+              <a:rot lat="0" lon="0" rev="0"/>
+            </a:camera>
+            <a:lightRig rig="threePt" dir="t">
+              <a:rot lat="0" lon="0" rev="1200000"/>
+            </a:lightRig>
+          </a:scene3d>
+          <a:sp3d>
+            <a:bevelT w="63500" h="25400"/>
+          </a:sp3d>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
+                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
+                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill>
+        <a:gradFill rotWithShape="1">
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
+                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
+                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
-          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
+  <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="true" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:A45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>ID MUESTRAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="n">
+        <v>2203798</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ERROR</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>2203840</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>2203841</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>2203842</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>2203909</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>2203910</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>2203911</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>2203912</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>2203913</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>2203914</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>2203915</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>2203916</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>2203917</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2203918</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2203920</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2203921</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2203922</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2203923</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2203924</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2203925</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2203926</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2203927</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2203928</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2203929</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2203930</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2203931</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2203932</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2203933</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2203934</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2203935</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2203936</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2203937</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2220091</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2220092</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2220093</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2220094</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2220095</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2220096</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2220097</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2220098</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2220099</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2220100</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2220101</v>
       </c>
     </row>
   </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
+  <autoFilter ref="A1:A45"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$48</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A45"/>
+  <dimension ref="A1:A48"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,8 +672,23 @@
         <v>2220101</v>
       </c>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2225271</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2225272</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2228150</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A45"/>
+  <autoFilter ref="A1:A48"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$15</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,244 +451,79 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="n">
-        <v>2203798</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>ERROR</t>
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>2298814</v>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2203840</v>
+        <v>2298815</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2203841</v>
+        <v>2298816</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2203842</v>
+        <v>2298817</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2203909</v>
+        <v>2298818</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2203910</v>
+        <v>2298830</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2203911</v>
+        <v>2298831</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2203912</v>
+        <v>2298832</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2203913</v>
+        <v>2298833</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2203914</v>
+        <v>2298834</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2203915</v>
+        <v>2298835</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2203916</v>
+        <v>2298836</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2203917</v>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="n">
-        <v>2203918</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="n">
-        <v>2203920</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="n">
-        <v>2203921</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="n">
-        <v>2203922</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="n">
-        <v>2203923</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="n">
-        <v>2203924</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="n">
-        <v>2203925</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="n">
-        <v>2203926</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="n">
-        <v>2203927</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="n">
-        <v>2203928</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="n">
-        <v>2203929</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="n">
-        <v>2203930</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="n">
-        <v>2203931</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="n">
-        <v>2203932</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="n">
-        <v>2203933</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="n">
-        <v>2203934</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="n">
-        <v>2203935</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="n">
-        <v>2203936</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="n">
-        <v>2203937</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="n">
-        <v>2220091</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="n">
-        <v>2220092</v>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="n">
-        <v>2220093</v>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="n">
-        <v>2220094</v>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="n">
-        <v>2220095</v>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="n">
-        <v>2220096</v>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="n">
-        <v>2220097</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="n">
-        <v>2220098</v>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="n">
-        <v>2220099</v>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="n">
-        <v>2220100</v>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="n">
-        <v>2220101</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="n">
-        <v>2225271</v>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="n">
-        <v>2225272</v>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="n">
-        <v>2228150</v>
+        <v>2298837</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A48"/>
+  <autoFilter ref="A1:A15"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$15</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$20</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A15"/>
+  <dimension ref="A1:A20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -522,8 +522,33 @@
         <v>2298837</v>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>2313570</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>2313571</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>2313572</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>2313573</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>2313574</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A15"/>
+  <autoFilter ref="A1:A20"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -9,7 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$48</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$51</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A48"/>
+  <dimension ref="A1:A51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -687,8 +687,23 @@
         <v>2228150</v>
       </c>
     </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2242676</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2242679</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2242680</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A48"/>
+  <autoFilter ref="A1:A51"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$20</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A20"/>
+  <dimension ref="A1:A39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -547,8 +547,103 @@
         <v>2313574</v>
       </c>
     </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>2377647</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>2377648</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>2377649</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>2377650</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>2377651</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>2377655</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>2377656</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>2377657</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>2377658</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>2377659</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>2377662</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>2377664</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>2377666</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>2377668</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>2377670</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>2377671</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>2377672</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>2377673</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>2377674</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A20"/>
+  <autoFilter ref="A1:A39"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$39</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$122</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A39"/>
+  <dimension ref="A1:A122"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -642,8 +642,423 @@
         <v>2377674</v>
       </c>
     </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>2391043</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>2391045</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>2391047</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>2391048</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>2391049</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>2391054</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>2391056</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>2391059</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>2391060</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>2391061</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>2391062</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>2391063</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>2391064</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>2391065</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>2391066</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>2391069</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>2391071</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>2391073</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>2391075</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>2391077</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>2391085</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>2391087</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>2391088</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>2391092</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>2391100</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>2391102</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>2391104</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>2391106</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>2391108</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>2391117</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>2391119</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>2391121</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>2391123</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>2391125</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>2391136</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>2391138</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>2391140</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>2391142</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>2391144</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>2391152</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>2391154</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>2391156</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>2391158</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>2391163</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>2391168</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>2391169</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>2391170</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>2391171</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>2391172</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>2391173</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>2391174</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>2391175</v>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>2391177</v>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>2391180</v>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>2391181</v>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>2391182</v>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>2391183</v>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>2391184</v>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>2391185</v>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>2391189</v>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>2391190</v>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="n">
+        <v>2391191</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="n">
+        <v>2391192</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="n">
+        <v>2391194</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="n">
+        <v>2391197</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="n">
+        <v>2391198</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="n">
+        <v>2391199</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="n">
+        <v>2391200</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="n">
+        <v>2391201</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="n">
+        <v>2391202</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>2391203</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>2391204</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>2391387</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>2391518</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>2391520</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>2391521</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>2391524</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>2391526</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>2391532</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>2391534</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>2391536</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>2391539</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>2391541</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:A39"/>
+  <autoFilter ref="A1:A122"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -9,7 +9,7 @@
     <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$122</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Sheet1'!$A$1:$A$113</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -440,7 +440,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A122"/>
+  <dimension ref="A1:A113"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -451,614 +451,567 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>ERROR</t>
-        </is>
+      <c r="A2" t="n">
+        <v>2420841</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>2298814</v>
+        <v>2420842</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>2298815</v>
+        <v>2420843</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>2298816</v>
+        <v>2420844</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>2298817</v>
+        <v>2420845</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>2298818</v>
+        <v>2420846</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>2298830</v>
+        <v>2420847</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2298831</v>
+        <v>2420849</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>2298832</v>
+        <v>2420850</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>2298833</v>
+        <v>2420851</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>2298834</v>
+        <v>2420852</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>2298835</v>
+        <v>2420853</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>2298836</v>
+        <v>2420854</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>2298837</v>
+        <v>2420855</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>2313570</v>
+        <v>2420856</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>2313571</v>
+        <v>2420857</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>2313572</v>
+        <v>2420858</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>2313573</v>
+        <v>2420859</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>2313574</v>
+        <v>2420860</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>2377647</v>
+        <v>2420861</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>2377648</v>
+        <v>2420865</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>2377649</v>
+        <v>2420866</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>2377650</v>
+        <v>2420867</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>2377651</v>
+        <v>2420868</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>2377655</v>
+        <v>2420869</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>2377656</v>
+        <v>2420870</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>2377657</v>
+        <v>2420871</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>2377658</v>
+        <v>2420873</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>2377659</v>
+        <v>2420876</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>2377662</v>
+        <v>2420877</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>2377664</v>
+        <v>2420881</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>2377666</v>
+        <v>2420883</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>2377668</v>
+        <v>2420884</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>2377670</v>
+        <v>2420885</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>2377671</v>
+        <v>2420886</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>2377672</v>
+        <v>2420890</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>2377673</v>
+        <v>2420892</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>2377674</v>
+        <v>2420893</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>2391043</v>
+        <v>2420894</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>2391045</v>
+        <v>2420896</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>2391047</v>
+        <v>2420899</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>2391048</v>
+        <v>2420901</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>2391049</v>
+        <v>2420903</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>2391054</v>
+        <v>2420905</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>2391056</v>
+        <v>2420906</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>2391059</v>
+        <v>2420908</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>2391060</v>
+        <v>2420910</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>2391061</v>
+        <v>2420911</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>2391062</v>
+        <v>2420912</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>2391063</v>
+        <v>2420914</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>2391064</v>
+        <v>2420916</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>2391065</v>
+        <v>2420918</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>2391066</v>
+        <v>2420920</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>2391069</v>
+        <v>2420922</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>2391071</v>
+        <v>2420924</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>2391073</v>
+        <v>2420926</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>2391075</v>
+        <v>2421201</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>2391077</v>
+        <v>2421202</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>2391085</v>
+        <v>2421203</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>2391087</v>
+        <v>2421204</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>2391088</v>
+        <v>2421205</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>2391092</v>
+        <v>2421208</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>2391100</v>
+        <v>2421210</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>2391102</v>
+        <v>2421211</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>2391104</v>
+        <v>2421212</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>2391106</v>
+        <v>2421213</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>2391108</v>
+        <v>2421214</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>2391117</v>
+        <v>2421215</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>2391119</v>
+        <v>2421216</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>2391121</v>
+        <v>2421217</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>2391123</v>
+        <v>2421218</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>2391125</v>
+        <v>2421219</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>2391136</v>
+        <v>2421220</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>2391138</v>
+        <v>2421221</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>2391140</v>
+        <v>2421222</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>2391142</v>
+        <v>2421223</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>2391144</v>
+        <v>2421224</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>2391152</v>
+        <v>2421225</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>2391154</v>
+        <v>2421226</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>2391156</v>
+        <v>2421227</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>2391158</v>
+        <v>2421228</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>2391163</v>
+        <v>2421229</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>2391168</v>
+        <v>2421230</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>2391169</v>
+        <v>2421231</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>2391170</v>
+        <v>2421232</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>2391171</v>
+        <v>2421233</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>2391172</v>
+        <v>2421234</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>2391173</v>
+        <v>2421235</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>2391174</v>
+        <v>2421236</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>2391175</v>
+        <v>2421237</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>2391177</v>
+        <v>2421238</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>2391180</v>
+        <v>2421239</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>2391181</v>
+        <v>2421240</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>2391182</v>
+        <v>2421241</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>2391183</v>
+        <v>2421242</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>2391184</v>
+        <v>2421243</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>2391185</v>
+        <v>2421247</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>2391189</v>
+        <v>2421248</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>2391190</v>
+        <v>2421249</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>2391191</v>
+        <v>2421252</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>2391192</v>
+        <v>2421253</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>2391194</v>
+        <v>2421255</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>2391197</v>
+        <v>2421256</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>2391198</v>
+        <v>2421257</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>2391199</v>
+        <v>2421258</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>2391200</v>
+        <v>2421259</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>2391201</v>
+        <v>2421264</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>2391202</v>
+        <v>2421266</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>2391203</v>
+        <v>2421267</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>2391204</v>
+        <v>2421269</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>2391387</v>
+        <v>2421271</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>2391518</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="n">
-        <v>2391520</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="n">
-        <v>2391521</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="n">
-        <v>2391524</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="n">
-        <v>2391526</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="n">
-        <v>2391532</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="n">
-        <v>2391534</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="n">
-        <v>2391536</v>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="n">
-        <v>2391539</v>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="n">
-        <v>2391541</v>
+        <v>2421272</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:A122"/>
+  <autoFilter ref="A1:A113"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Registros Pendientes/RegistroAuxiliar.xlsx
+++ b/Registros Pendientes/RegistroAuxiliar.xlsx
@@ -1,43 +1,76 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
-  <workbookPr defaultThemeVersion="124226"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2">
+  <fileVersion appName="Calc"/>
+  <workbookPr backupFile="false" showObjects="all" date1904="false"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
+  <extLst>
+    <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
+      <loext:extCalcPr stringRefSyntax="ExcelA1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1" uniqueCount="1">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>ID MUESTRAS</t>
+    <t xml:space="preserve">ID MUESTRAS</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1974308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1974873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2027482</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="General"/>
+  </numFmts>
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <name val="Arial"/>
+      <family val="0"/>
+    </font>
+    <font>
+      <b val="true"/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -49,82 +82,103 @@
     </fill>
   </fills>
   <borders count="2">
-    <border>
+    <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+    <border diagonalUp="false" diagonalDown="false">
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+  <cellStyleXfs count="20">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="43" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="41" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
+    <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Comma" xfId="15" builtinId="3"/>
+    <cellStyle name="Comma [0]" xfId="16" builtinId="6"/>
+    <cellStyle name="Currency" xfId="17" builtinId="4"/>
+    <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
+    <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <dxfs count="0"/>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:srgbClr val="000000"/>
       </a:dk1>
       <a:lt1>
-        <a:sysClr val="window" lastClr="FFFFFF"/>
+        <a:srgbClr val="ffffff"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="1F497D"/>
+        <a:srgbClr val="1f497d"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="EEECE1"/>
+        <a:srgbClr val="eeece1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4F81BD"/>
+        <a:srgbClr val="4f81bd"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="C0504D"/>
+        <a:srgbClr val="c0504d"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="9BBB59"/>
+        <a:srgbClr val="9bbb59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="8064A2"/>
+        <a:srgbClr val="8064a2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="4BACC6"/>
+        <a:srgbClr val="4bacc6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="F79646"/>
+        <a:srgbClr val="f79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0000FF"/>
+        <a:srgbClr val="0000ff"/>
       </a:hlink>
       <a:folHlink>
         <a:srgbClr val="800080"/>
@@ -132,257 +186,173 @@
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Cambria"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Times New Roman"/>
-        <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="MoolBoran"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Times New Roman"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
-        <a:font script="Arab" typeface="Arial"/>
-        <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
-        <a:font script="Ethi" typeface="Nyala"/>
-        <a:font script="Beng" typeface="Vrinda"/>
-        <a:font script="Gujr" typeface="Shruti"/>
-        <a:font script="Khmr" typeface="DaunPenh"/>
-        <a:font script="Knda" typeface="Tunga"/>
-        <a:font script="Guru" typeface="Raavi"/>
-        <a:font script="Cans" typeface="Euphemia"/>
-        <a:font script="Cher" typeface="Plantagenet Cherokee"/>
-        <a:font script="Yiii" typeface="Microsoft Yi Baiti"/>
-        <a:font script="Tibt" typeface="Microsoft Himalaya"/>
-        <a:font script="Thaa" typeface="MV Boli"/>
-        <a:font script="Deva" typeface="Mangal"/>
-        <a:font script="Telu" typeface="Gautami"/>
-        <a:font script="Taml" typeface="Latha"/>
-        <a:font script="Syrc" typeface="Estrangelo Edessa"/>
-        <a:font script="Orya" typeface="Kalinga"/>
-        <a:font script="Mlym" typeface="Kartika"/>
-        <a:font script="Laoo" typeface="DokChampa"/>
-        <a:font script="Sinh" typeface="Iskoola Pota"/>
-        <a:font script="Mong" typeface="Mongolian Baiti"/>
-        <a:font script="Viet" typeface="Arial"/>
-        <a:font script="Uigh" typeface="Microsoft Uighur"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme>
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="50000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="35000">
               <a:schemeClr val="phClr">
                 <a:tint val="37000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:tint val="15000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="1"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:shade val="51000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="80000">
               <a:schemeClr val="phClr">
                 <a:shade val="93000"/>
-                <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="94000"/>
-                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:lin ang="16200000" scaled="0"/>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
         <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr">
-              <a:shade val="95000"/>
-              <a:satMod val="105000"/>
-            </a:schemeClr>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
         <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
           <a:prstDash val="solid"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="20000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="38000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
+          <a:effectLst/>
         </a:effectStyle>
         <a:effectStyle>
-          <a:effectLst>
-            <a:outerShdw blurRad="40000" dist="23000" dir="5400000" rotWithShape="0">
-              <a:srgbClr val="000000">
-                <a:alpha val="35000"/>
-              </a:srgbClr>
-            </a:outerShdw>
-          </a:effectLst>
-          <a:scene3d>
-            <a:camera prst="orthographicFront">
-              <a:rot lat="0" lon="0" rev="0"/>
-            </a:camera>
-            <a:lightRig rig="threePt" dir="t">
-              <a:rot lat="0" lon="0" rev="1200000"/>
-            </a:lightRig>
-          </a:scene3d>
-          <a:sp3d>
-            <a:bevelT w="63500" h="25400"/>
-          </a:sp3d>
+          <a:effectLst/>
         </a:effectStyle>
       </a:effectStyleLst>
       <a:bgFillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="40000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="40000">
               <a:schemeClr val="phClr">
                 <a:tint val="45000"/>
                 <a:shade val="99000"/>
-                <a:satMod val="350000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="20000"/>
-                <a:satMod val="255000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
-        <a:gradFill rotWithShape="1">
+        <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
                 <a:tint val="80000"/>
-                <a:satMod val="300000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
                 <a:shade val="30000"/>
-                <a:satMod val="200000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
           <a:path path="circle">
             <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
           </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+  <sheetPr filterMode="false">
+    <pageSetUpPr fitToPage="false"/>
+  </sheetPr>
+  <dimension ref="A1:A4"/>
+  <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" spans="1:1">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
     </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="0" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="0" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="0" t="s">
+        <v>3</v>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <headerFooter differentFirst="false" differentOddEven="false">
+    <oddHeader/>
+    <oddFooter/>
+  </headerFooter>
 </worksheet>
 </file>